--- a/static/templates/vulnerability_template.xlsx
+++ b/static/templates/vulnerability_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\grc_backend\static\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cydea\grc_backend\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA94A83A-86B0-4D05-941C-B08A4E121182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E48B625-9439-406C-9DE3-AA342BE86185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D6B5BE0-4B82-4B47-B54C-FC652D93DE65}"/>
   </bookViews>
@@ -129,8 +129,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -149,9 +150,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -189,7 +190,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -295,7 +296,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -437,7 +438,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -447,12 +448,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA41C066-4864-40C6-9505-396514F2727C}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="8.88671875" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -460,7 +464,7 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -468,7 +472,7 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -476,7 +480,7 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -484,7 +488,7 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -492,7 +496,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -500,7 +504,7 @@
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -508,7 +512,7 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -516,7 +520,7 @@
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -524,7 +528,7 @@
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -532,7 +536,7 @@
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -540,7 +544,7 @@
       <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -548,7 +552,7 @@
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -556,7 +560,7 @@
       <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
     </row>
